--- a/aula03 excel/atividade controle de faltas.xlsx
+++ b/aula03 excel/atividade controle de faltas.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aluno\Documents\GitHub\karlos henrique\aula03 excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C39B0A93-89FF-4DA2-A601-9D89701C9F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BA90296-7DDA-467B-864E-FBFE920EF075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{D0577ABE-FF5B-4603-BC6A-1DDA25986E9A}"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
-    <sheet name="Planilha1 (2)" sheetId="2" r:id="rId2"/>
-    <sheet name="Planilha1 (3)" sheetId="3" r:id="rId3"/>
+    <sheet name="Faltas Turma A" sheetId="1" r:id="rId1"/>
+    <sheet name="Faltas turmas B" sheetId="2" r:id="rId2"/>
+    <sheet name="Total de Faltas" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -236,7 +236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -244,17 +244,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -262,6 +252,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -589,14 +588,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
@@ -909,14 +908,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
@@ -1230,302 +1229,298 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="D3" s="5" t="s">
+      <c r="B3" s="8"/>
+      <c r="D3" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="4"/>
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="9">
-        <f>Planilha1!F4</f>
+      <c r="A5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="5">
+        <f>'Faltas Turma A'!F4</f>
         <v>11</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="9">
-        <f>'Planilha1 (2)'!F4</f>
+      <c r="E5" s="5">
+        <f>'Faltas turmas B'!F4</f>
         <v>7</v>
       </c>
-      <c r="F5" s="4"/>
+      <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="9">
-        <f>Planilha1!F5</f>
-        <v>6</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="B6" s="5">
+        <f>'Faltas Turma A'!F5</f>
+        <v>6</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="9">
-        <f>'Planilha1 (2)'!F5</f>
-        <v>3</v>
-      </c>
-      <c r="F6" s="4"/>
+      <c r="E6" s="5">
+        <f>'Faltas turmas B'!F5</f>
+        <v>3</v>
+      </c>
+      <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" s="9">
-        <f>Planilha1!F6</f>
-        <v>6</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="A7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="5">
+        <f>'Faltas Turma A'!F6</f>
+        <v>6</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="9">
-        <f>'Planilha1 (2)'!F6</f>
-        <v>6</v>
-      </c>
-      <c r="F7" s="4"/>
+      <c r="E7" s="5">
+        <f>'Faltas turmas B'!F6</f>
+        <v>6</v>
+      </c>
+      <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="9">
-        <f>Planilha1!F7</f>
-        <v>3</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="B8" s="5">
+        <f>'Faltas Turma A'!F7</f>
+        <v>3</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="9">
-        <f>'Planilha1 (2)'!F7</f>
+      <c r="E8" s="5">
+        <f>'Faltas turmas B'!F7</f>
         <v>8</v>
       </c>
-      <c r="F8" s="4"/>
+      <c r="F8" s="3"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="9">
-        <f>Planilha1!F8</f>
+      <c r="B9" s="5">
+        <f>'Faltas Turma A'!F8</f>
         <v>8</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="9">
-        <f>'Planilha1 (2)'!F8</f>
+      <c r="E9" s="5">
+        <f>'Faltas turmas B'!F8</f>
         <v>13</v>
       </c>
-      <c r="F9" s="4"/>
+      <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="9">
-        <f>Planilha1!F9</f>
+      <c r="B10" s="5">
+        <f>'Faltas Turma A'!F9</f>
         <v>12</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="9">
-        <f>'Planilha1 (2)'!F9</f>
-        <v>6</v>
-      </c>
-      <c r="F10" s="4"/>
+      <c r="E10" s="5">
+        <f>'Faltas turmas B'!F9</f>
+        <v>6</v>
+      </c>
+      <c r="F10" s="3"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="9">
-        <f>Planilha1!F10</f>
+      <c r="A11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="5">
+        <f>'Faltas Turma A'!F10</f>
         <v>5</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="9">
-        <f>'Planilha1 (2)'!F10</f>
+      <c r="E11" s="5">
+        <f>'Faltas turmas B'!F10</f>
         <v>14</v>
       </c>
-      <c r="F11" s="4"/>
+      <c r="F11" s="3"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="9">
-        <f>Planilha1!F11</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="B12" s="5">
+        <f>'Faltas Turma A'!F11</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="9">
-        <f>'Planilha1 (2)'!F11</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="4"/>
+      <c r="E12" s="5">
+        <f>'Faltas turmas B'!F11</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="3"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="9">
-        <f>Planilha1!F12</f>
+      <c r="B13" s="5">
+        <f>'Faltas Turma A'!F12</f>
         <v>22</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="9">
-        <f>'Planilha1 (2)'!F12</f>
+      <c r="E13" s="5">
+        <f>'Faltas turmas B'!F12</f>
         <v>4</v>
       </c>
-      <c r="F13" s="4"/>
+      <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="9">
-        <f>Planilha1!F13</f>
+      <c r="B14" s="5">
+        <f>'Faltas Turma A'!F13</f>
         <v>10</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E14" s="9">
-        <f>'Planilha1 (2)'!F13</f>
-        <v>3</v>
-      </c>
-      <c r="F14" s="4"/>
+      <c r="E14" s="5">
+        <f>'Faltas turmas B'!F13</f>
+        <v>3</v>
+      </c>
+      <c r="F14" s="3"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="9">
-        <f>Planilha1!F14</f>
+      <c r="B15" s="5">
+        <f>'Faltas Turma A'!F14</f>
         <v>8</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="9">
-        <f>'Planilha1 (2)'!F14</f>
-        <v>6</v>
-      </c>
-      <c r="F15" s="4"/>
+      <c r="E15" s="5">
+        <f>'Faltas turmas B'!F14</f>
+        <v>6</v>
+      </c>
+      <c r="F15" s="3"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="9">
-        <f>Planilha1!F15</f>
+      <c r="B16" s="5">
+        <f>'Faltas Turma A'!F15</f>
         <v>16</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E16" s="9">
-        <f>'Planilha1 (2)'!F15</f>
+      <c r="E16" s="5">
+        <f>'Faltas turmas B'!F15</f>
         <v>8</v>
       </c>
-      <c r="F16" s="4"/>
+      <c r="F16" s="3"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="9">
-        <f>Planilha1!F16</f>
+      <c r="B17" s="5">
+        <f>'Faltas Turma A'!F16</f>
         <v>18</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E17" s="9">
-        <f>'Planilha1 (2)'!F16</f>
+      <c r="E17" s="5">
+        <f>'Faltas turmas B'!F16</f>
         <v>7</v>
       </c>
-      <c r="F17" s="4"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
+      <c r="F17" s="3"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="9">
+      <c r="B19" s="5">
         <f>MAX(B5:B18)</f>
         <v>22</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="6">
         <f>MAX(E5:E18)</f>
         <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="9">
+      <c r="B20" s="5">
         <f>MIN(B5:B17)</f>
         <v>0</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="5">
         <f>MIN(E5:E17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="6">
         <f>AVERAGE(B5:B17)</f>
         <v>9.615384615384615</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="6">
         <f>AVERAGE(E5:E17)</f>
         <v>6.5384615384615383</v>
       </c>
